--- a/results/tables/pca_scores_site_conditional.xlsx
+++ b/results/tables/pca_scores_site_conditional.xlsx
@@ -1,197 +1,190 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/lf649_drexel_edu/Documents/Research/South Philly R21/Papers/Analysis Paper/thriveair_analysis/results/tables/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_CE1A1223007967BAB68AD699423D01F6325C4499" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE70481C-E228-4A94-AF1E-3283F6A9EB28}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2820" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PCA Scores" sheetId="1" r:id="rId1"/>
+    <sheet name="PCA Scores" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="55">
-  <si>
-    <t>site</t>
-  </si>
-  <si>
-    <t>site_type</t>
-  </si>
-  <si>
-    <t>land_use</t>
-  </si>
-  <si>
-    <t>industrial_20</t>
-  </si>
-  <si>
-    <t>site_traffic</t>
-  </si>
-  <si>
-    <t>Component_1</t>
-  </si>
-  <si>
-    <t>Component_2</t>
-  </si>
-  <si>
-    <t>Component_3</t>
-  </si>
-  <si>
-    <t>Component_4</t>
-  </si>
-  <si>
-    <t>nearby_sources</t>
-  </si>
-  <si>
-    <t>31st &amp; Grays Ferry</t>
-  </si>
-  <si>
-    <t>Community</t>
-  </si>
-  <si>
-    <t>Commercial</t>
-  </si>
-  <si>
-    <t>Industrial</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Fire station</t>
-  </si>
-  <si>
-    <t>61st &amp; Passyunk</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>Auto body shop, junkyard, gas station</t>
-  </si>
-  <si>
-    <t>Essington &amp; Mingo</t>
-  </si>
-  <si>
-    <t>Auto body shop, junkyard</t>
-  </si>
-  <si>
-    <t>26th &amp; Hartranft</t>
-  </si>
-  <si>
-    <t>Vacant</t>
-  </si>
-  <si>
-    <t>Diesel corridor, portable toilet supplier</t>
-  </si>
-  <si>
-    <t>28th &amp; Passyunk</t>
-  </si>
-  <si>
-    <t>Oil terminal, gas station, former refinery site, natural gas terminal</t>
-  </si>
-  <si>
-    <t>25th &amp; Point Breeze</t>
-  </si>
-  <si>
-    <t>Institution</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Finnegan Playground</t>
-  </si>
-  <si>
-    <t>Mixed Use</t>
-  </si>
-  <si>
-    <t>Commissary kitchen</t>
-  </si>
-  <si>
-    <t>Crescent Park</t>
-  </si>
-  <si>
-    <t>Open Space</t>
-  </si>
-  <si>
-    <t>FedEx warehouse, municipal waste transfer station</t>
-  </si>
-  <si>
-    <t>Snyder &amp; Vare</t>
-  </si>
-  <si>
-    <t>Non-Industrial</t>
-  </si>
-  <si>
-    <t>Auto body shop</t>
-  </si>
-  <si>
-    <t>Universal Charter School at Vare</t>
-  </si>
-  <si>
-    <t>Splash pad</t>
-  </si>
-  <si>
-    <t>Vare &amp; New Hope</t>
-  </si>
-  <si>
-    <t>Car dealer, auto body shop</t>
-  </si>
-  <si>
-    <t>29th &amp; Moore</t>
-  </si>
-  <si>
-    <t>Residential</t>
-  </si>
-  <si>
-    <t>24th &amp; Ritner</t>
-  </si>
-  <si>
-    <t>Carl Moore Health Center</t>
-  </si>
-  <si>
-    <t>Medical clinic</t>
-  </si>
-  <si>
-    <t>Bartram’s Garden</t>
-  </si>
-  <si>
-    <t>Wharton Park</t>
-  </si>
-  <si>
-    <t>Recreation</t>
-  </si>
-  <si>
-    <t>Audenreid School</t>
-  </si>
-  <si>
-    <t>Hartranft &amp; Pietro Wy</t>
-  </si>
-  <si>
-    <t>28th &amp; Point Breeze</t>
-  </si>
-  <si>
-    <t>Laundromat</t>
-  </si>
-  <si>
-    <t>Morris &amp; Point Breeze</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+  <si>
+    <t xml:space="preserve">site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">site_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">land_use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">industrial_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">site_traffic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nearby_sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31st &amp; Grays Ferry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61st &amp; Passyunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto body shop, junkyard, gas station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essington &amp; Mingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto body shop, junkyard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26th &amp; Hartranft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diesel corridor, portable toilet supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28th &amp; Passyunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil terminal, gas station, former refinery site, natural gas terminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25th &amp; Point Breeze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnegan Playground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commissary kitchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crescent Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FedEx warehouse, municipal waste transfer station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snyder &amp; Vare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Industrial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto body shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal Charter School at Vare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splash pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vare &amp; New Hope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car dealer, auto body shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29th &amp; Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24th &amp; Ritner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carl Moore Health Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical clinic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bartram’s Garden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wharton Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recreation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audenreid School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hartranft &amp; Pietro Wy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28th &amp; Point Breeze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laundromat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morris &amp; Point Breeze</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -227,15 +220,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -517,15 +501,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,7 +537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -573,23 +553,23 @@
       <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>-0.62</v>
-      </c>
-      <c r="G2">
-        <v>-1.24</v>
-      </c>
-      <c r="H2">
-        <v>-0.21</v>
-      </c>
-      <c r="I2">
-        <v>0.04</v>
+      <c r="F2" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.13</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -605,23 +585,23 @@
       <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="F3">
-        <v>0.88</v>
-      </c>
-      <c r="G3">
-        <v>0.39</v>
-      </c>
-      <c r="H3">
-        <v>0.08</v>
-      </c>
-      <c r="I3">
-        <v>0.94</v>
+      <c r="F3" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.7</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -637,23 +617,23 @@
       <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="F4">
-        <v>-1.32</v>
-      </c>
-      <c r="G4">
-        <v>-1.01</v>
-      </c>
-      <c r="H4">
-        <v>-0.38</v>
-      </c>
-      <c r="I4">
-        <v>0.78</v>
+      <c r="F4" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.11</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -669,23 +649,23 @@
       <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="F5">
-        <v>0.79</v>
-      </c>
-      <c r="G5">
-        <v>1.49</v>
-      </c>
-      <c r="H5">
-        <v>0.68</v>
-      </c>
-      <c r="I5">
-        <v>-1.7</v>
+      <c r="F5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.87</v>
       </c>
       <c r="J5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -701,23 +681,23 @@
       <c r="E6" t="s">
         <v>14</v>
       </c>
-      <c r="F6">
-        <v>5.62</v>
-      </c>
-      <c r="G6">
-        <v>4.22</v>
-      </c>
-      <c r="H6">
-        <v>-0.01</v>
-      </c>
-      <c r="I6">
-        <v>-0.49</v>
+      <c r="F6" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.33</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -733,23 +713,23 @@
       <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="F7">
-        <v>-0.88</v>
-      </c>
-      <c r="G7">
-        <v>-0.67</v>
-      </c>
-      <c r="H7">
+      <c r="F7" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.81</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="I7" t="n">
         <v>-0.26</v>
-      </c>
-      <c r="I7">
-        <v>0.47</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -765,23 +745,23 @@
       <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="F8">
-        <v>-1.19</v>
-      </c>
-      <c r="G8">
-        <v>-1.25</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.34</v>
+      <c r="F8" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.28</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -797,23 +777,23 @@
       <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="F9">
-        <v>-3.1</v>
-      </c>
-      <c r="G9">
-        <v>-1.83</v>
-      </c>
-      <c r="H9">
-        <v>0.03</v>
-      </c>
-      <c r="I9">
-        <v>-0.3</v>
+      <c r="F9" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.85</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -829,23 +809,23 @@
       <c r="E10" t="s">
         <v>14</v>
       </c>
-      <c r="F10">
-        <v>-0.68</v>
-      </c>
-      <c r="G10">
-        <v>-0.51</v>
-      </c>
-      <c r="H10">
-        <v>-0.43</v>
-      </c>
-      <c r="I10">
-        <v>-0.17</v>
+      <c r="F10" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.18</v>
       </c>
       <c r="J10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -861,23 +841,23 @@
       <c r="E11" t="s">
         <v>14</v>
       </c>
-      <c r="F11">
-        <v>-0.32</v>
-      </c>
-      <c r="G11">
-        <v>-0.63</v>
-      </c>
-      <c r="H11">
-        <v>1.55</v>
-      </c>
-      <c r="I11">
-        <v>-0.21</v>
+      <c r="F11" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.05</v>
       </c>
       <c r="J11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -893,23 +873,23 @@
       <c r="E12" t="s">
         <v>14</v>
       </c>
-      <c r="F12">
-        <v>-0.83</v>
-      </c>
-      <c r="G12">
-        <v>-0.95</v>
-      </c>
-      <c r="H12">
-        <v>-0.18</v>
-      </c>
-      <c r="I12">
-        <v>0.26</v>
+      <c r="F12" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.22</v>
       </c>
       <c r="J12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -925,20 +905,21 @@
       <c r="E13" t="s">
         <v>14</v>
       </c>
-      <c r="F13">
-        <v>-0.85</v>
-      </c>
-      <c r="G13">
-        <v>-0.96</v>
-      </c>
-      <c r="H13">
-        <v>0.05</v>
-      </c>
-      <c r="I13">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J13"/>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -954,23 +935,23 @@
       <c r="E14" t="s">
         <v>14</v>
       </c>
-      <c r="F14">
-        <v>-0.45</v>
-      </c>
-      <c r="G14">
-        <v>-0.41</v>
-      </c>
-      <c r="H14">
-        <v>0.12</v>
-      </c>
-      <c r="I14">
-        <v>-0.3</v>
+      <c r="F14" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.33</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -986,23 +967,23 @@
       <c r="E15" t="s">
         <v>28</v>
       </c>
-      <c r="F15">
-        <v>-2.1</v>
-      </c>
-      <c r="G15">
-        <v>-1.05</v>
-      </c>
-      <c r="H15">
-        <v>0.09</v>
-      </c>
-      <c r="I15">
-        <v>-0.35</v>
+      <c r="F15" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.71</v>
       </c>
       <c r="J15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1018,20 +999,21 @@
       <c r="E16" t="s">
         <v>28</v>
       </c>
-      <c r="F16">
-        <v>-1.9</v>
-      </c>
-      <c r="G16">
-        <v>-1.66</v>
-      </c>
-      <c r="H16">
-        <v>-0.17</v>
-      </c>
-      <c r="I16">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F16" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J16"/>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1047,20 +1029,21 @@
       <c r="E17" t="s">
         <v>28</v>
       </c>
-      <c r="F17">
-        <v>-1.55</v>
-      </c>
-      <c r="G17">
-        <v>-1.48</v>
-      </c>
-      <c r="H17">
-        <v>-0.25</v>
-      </c>
-      <c r="I17">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F17" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J17"/>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1076,20 +1059,21 @@
       <c r="E18" t="s">
         <v>28</v>
       </c>
-      <c r="F18">
-        <v>-0.84</v>
-      </c>
-      <c r="G18">
-        <v>-0.18</v>
-      </c>
-      <c r="H18">
-        <v>0.1</v>
-      </c>
-      <c r="I18">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F18" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.56</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J18"/>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1105,20 +1089,21 @@
       <c r="E19" t="s">
         <v>28</v>
       </c>
-      <c r="F19">
-        <v>-1.17</v>
-      </c>
-      <c r="G19">
-        <v>-0.94</v>
-      </c>
-      <c r="H19">
-        <v>-1.02</v>
-      </c>
-      <c r="I19">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F19" t="n">
+        <v>-0.81</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J19"/>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1134,23 +1119,23 @@
       <c r="E20" t="s">
         <v>28</v>
       </c>
-      <c r="F20">
-        <v>-0.54</v>
-      </c>
-      <c r="G20">
-        <v>-0.45</v>
-      </c>
-      <c r="H20">
-        <v>0.09</v>
-      </c>
-      <c r="I20">
-        <v>0.2</v>
+      <c r="F20" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.06</v>
       </c>
       <c r="J20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1166,26 +1151,37 @@
       <c r="E21" t="s">
         <v>28</v>
       </c>
-      <c r="F21">
-        <v>-1.02</v>
-      </c>
-      <c r="G21">
-        <v>-0.86</v>
-      </c>
-      <c r="H21">
-        <v>-0.1</v>
-      </c>
-      <c r="I21">
-        <v>-0.09</v>
-      </c>
+      <c r="F21" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J21"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:XFD21">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="2:21">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="-1.7"/>
+        <cfvo type="num" val="-2.63"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.94"/>
+        <cfvo type="num" val="5.15"/>
+        <color rgb="FF086788"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFDD1C1A"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="-1.51"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4.15"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1193,29 +1189,19 @@
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="num" val="-1.02"/>
+        <cfvo type="num" val="-0.73"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1.55"/>
+        <cfvo type="num" val="0.76"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="-1.83"/>
+        <cfvo type="num" val="-1.33"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="4.22"/>
-        <color rgb="FF086788"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFDD1C1A"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="-3.1"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5.62"/>
+        <cfvo type="num" val="0.87"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1223,6 +1209,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/results/tables/pca_scores_site_conditional.xlsx
+++ b/results/tables/pca_scores_site_conditional.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">site</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t xml:space="preserve">nearby_sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component_5</t>
   </si>
   <si>
     <t xml:space="preserve">31st &amp; Grays Ferry</t>
@@ -536,642 +539,715 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.72</v>
+        <v>-0.63</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.71</v>
+        <v>-1.05</v>
       </c>
       <c r="H2" t="n">
         <v>-0.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.69</v>
+        <v>0.89</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.22</v>
+        <v>0.74</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7</v>
+        <v>-0.18</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.07</v>
+        <v>-1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.31</v>
+        <v>-1.04</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.21</v>
+        <v>0.13</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.11</v>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="G5" t="n">
-        <v>1.98</v>
+        <v>1.16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.39</v>
+        <v>-0.11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.87</v>
+        <v>-1.36</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="G6" t="n">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="H6" t="n">
-        <v>0.76</v>
+        <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.33</v>
+        <v>-2.09</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.78</v>
+        <v>-0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.81</v>
+        <v>-0.55</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.21</v>
+        <v>0.12</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.26</v>
+        <v>0.49</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
       <c r="F8" t="n">
-        <v>-1.26</v>
+        <v>-0.97</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.85</v>
+        <v>-1.34</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.44</v>
+        <v>0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.28</v>
+        <v>1.33</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.63</v>
+        <v>-2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.51</v>
+        <v>-1.85</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.62</v>
+        <v>-0.29</v>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>1.21</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.75</v>
+        <v>-0.62</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.34</v>
+        <v>-0.55</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="I10" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="J10" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.46</v>
+        <v>-0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.86</v>
+        <v>-0.81</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.82</v>
+        <v>-1.01</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07</v>
+        <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8</v>
+        <v>-0.86</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.75</v>
+        <v>-1.04</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.11</v>
+        <v>-0.37</v>
       </c>
       <c r="I13" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="J13"/>
+      <c r="K13" t="n">
+        <v>-0.23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.16</v>
+        <v>-0.27</v>
       </c>
       <c r="I14" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.67</v>
+        <v>-1.72</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.85</v>
+        <v>-0.9</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.42</v>
+        <v>-0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="J15" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.55</v>
+        <v>-1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.41</v>
+        <v>-1.7</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.27</v>
+        <v>-0.35</v>
       </c>
       <c r="I16" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="J16"/>
+      <c r="K16" t="n">
+        <v>-0.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.38</v>
+        <v>-1.34</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.97</v>
+        <v>-1.54</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.37</v>
+        <v>0.83</v>
       </c>
       <c r="J17"/>
+      <c r="K17" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.48</v>
+        <v>-0.61</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.56</v>
+        <v>0.52</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.26</v>
+        <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.13</v>
+        <v>-0.04</v>
       </c>
       <c r="J18"/>
+      <c r="K18" t="n">
+        <v>-0.68</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.81</v>
+        <v>-1.12</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.89</v>
+        <v>-0.8</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.73</v>
+        <v>-0.85</v>
       </c>
       <c r="I19" t="n">
-        <v>0.63</v>
+        <v>0.01</v>
       </c>
       <c r="J19"/>
+      <c r="K19" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.55</v>
+        <v>-0.37</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.07</v>
+        <v>0.05</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="J20" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.88</v>
+        <v>-0.78</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.63</v>
+        <v>-0.86</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="I21" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="J21"/>
+      <c r="K21" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="2:21">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="-2.8"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4.93"/>
+        <color rgb="FF086788"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFDD1C1A"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="-2.63"/>
+        <cfvo type="num" val="-1.85"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5.15"/>
+        <cfvo type="num" val="3.82"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1179,9 +1255,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="num" val="-1.51"/>
+        <cfvo type="num" val="-0.85"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="4.15"/>
+        <cfvo type="num" val="0.5"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1189,9 +1265,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="num" val="-0.73"/>
+        <cfvo type="num" val="-2.09"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.76"/>
+        <cfvo type="num" val="1.33"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1199,9 +1275,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="-1.33"/>
+        <cfvo type="num" val="-0.83"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.87"/>
+        <cfvo type="num" val="1.96"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>

--- a/results/tables/pca_scores_site_conditional.xlsx
+++ b/results/tables/pca_scores_site_conditional.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve">site</t>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t xml:space="preserve">nearby_sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component_5</t>
   </si>
   <si>
     <t xml:space="preserve">31st &amp; Grays Ferry</t>
@@ -539,715 +536,642 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-0.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-0.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J4" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="J5" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="J6" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
       <c r="F7" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.55</v>
+        <v>-0.63</v>
       </c>
       <c r="H7" t="n">
-        <v>0.12</v>
+        <v>0.07</v>
       </c>
       <c r="I7" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.56</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J8" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J9" t="s">
         <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J10" t="s">
         <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J10" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J11" t="s">
         <v>39</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J11" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J12" t="s">
         <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.81</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J12" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.86</v>
+        <v>-0.89</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.04</v>
+        <v>-0.97</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.37</v>
+        <v>-0.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="J13"/>
-      <c r="K13" t="n">
-        <v>-0.23</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="I14" t="n">
         <v>-0.01</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="J15" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J15" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.77</v>
+        <v>-1.92</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.35</v>
+        <v>-0.24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.83</v>
+        <v>0.34</v>
       </c>
       <c r="J16"/>
-      <c r="K16" t="n">
-        <v>-0.39</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
         <v>49</v>
       </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.34</v>
+        <v>-1.54</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.54</v>
+        <v>-1.39</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.28</v>
+        <v>-0.22</v>
       </c>
       <c r="I17" t="n">
-        <v>0.83</v>
+        <v>0.17</v>
       </c>
       <c r="J17"/>
-      <c r="K17" t="n">
-        <v>-0.1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.61</v>
+        <v>-0.64</v>
       </c>
       <c r="G18" t="n">
-        <v>0.52</v>
+        <v>-0.06</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.04</v>
+        <v>0.3</v>
       </c>
       <c r="J18"/>
-      <c r="K18" t="n">
-        <v>-0.68</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
         <v>-1.12</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8</v>
+        <v>-0.87</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="J19"/>
-      <c r="K19" t="n">
-        <v>-0.38</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J20" t="s">
         <v>53</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J20" t="s">
-        <v>54</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-0.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="G21" t="n">
         <v>-0.78</v>
       </c>
-      <c r="G21" t="n">
-        <v>-0.86</v>
-      </c>
       <c r="H21" t="n">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="I21" t="n">
-        <v>0.59</v>
+        <v>0.08</v>
       </c>
       <c r="J21"/>
-      <c r="K21" t="n">
-        <v>-0.02</v>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="2:21">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="num" val="-2.8"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="4.93"/>
-        <color rgb="FF086788"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFDD1C1A"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="-1.85"/>
+        <cfvo type="num" val="-3.19"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="3.82"/>
+        <cfvo type="num" val="5.57"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1255,9 +1179,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="num" val="-0.85"/>
+        <cfvo type="num" val="-1.63"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="3.96"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1265,9 +1189,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="num" val="-2.09"/>
+        <cfvo type="num" val="-0.84"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1.33"/>
+        <cfvo type="num" val="0.37"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1275,9 +1199,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="-0.83"/>
+        <cfvo type="num" val="-1.96"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1.96"/>
+        <cfvo type="num" val="0.84"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>

--- a/results/tables/pca_scores_site_conditional.xlsx
+++ b/results/tables/pca_scores_site_conditional.xlsx
@@ -557,13 +557,13 @@
         <v>-0.74</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.11</v>
+        <v>-1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -586,16 +586,16 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="G3" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="I3" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -618,16 +618,16 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.38</v>
+        <v>-1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
@@ -650,16 +650,16 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.96</v>
+        <v>-1.95</v>
       </c>
       <c r="J5" t="s">
         <v>23</v>
@@ -682,16 +682,16 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>5.57</v>
+        <v>5.58</v>
       </c>
       <c r="G6" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.11</v>
+        <v>-1.07</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -714,16 +714,16 @@
         <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8</v>
+        <v>-0.81</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.63</v>
+        <v>-0.66</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
@@ -749,13 +749,13 @@
         <v>-1.29</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.15</v>
+        <v>-1.21</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.58</v>
+        <v>0.56</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
@@ -778,16 +778,16 @@
         <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.19</v>
+        <v>-3.18</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.63</v>
+        <v>-1.68</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -810,16 +810,16 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="s">
         <v>37</v>
@@ -842,16 +842,16 @@
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="s">
         <v>39</v>
@@ -874,16 +874,16 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.94</v>
+        <v>-0.97</v>
       </c>
       <c r="H12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J12" t="s">
         <v>41</v>
@@ -906,16 +906,16 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.97</v>
+        <v>-1.01</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J13"/>
     </row>
@@ -936,13 +936,13 @@
         <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.39</v>
+        <v>-0.41</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="I14" t="n">
         <v>-0.01</v>
@@ -968,16 +968,16 @@
         <v>28</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.97</v>
+        <v>-1.99</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.95</v>
+        <v>-0.98</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="J15" t="s">
         <v>46</v>
@@ -1000,16 +1000,16 @@
         <v>28</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.92</v>
+        <v>-1.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6</v>
+        <v>-1.63</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="I16" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J16"/>
     </row>
@@ -1030,16 +1030,16 @@
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.54</v>
+        <v>-1.53</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.39</v>
+        <v>-1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="I17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J17"/>
     </row>
@@ -1060,16 +1060,16 @@
         <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.64</v>
+        <v>-0.71</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="J18"/>
     </row>
@@ -1090,16 +1090,16 @@
         <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.12</v>
+        <v>-1.14</v>
       </c>
       <c r="G19" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H19" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H19" t="n">
-        <v>-0.84</v>
-      </c>
       <c r="I19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J19"/>
     </row>
@@ -1120,13 +1120,13 @@
         <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0.32</v>
@@ -1152,16 +1152,16 @@
         <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.78</v>
+        <v>-0.81</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="J21"/>
     </row>
@@ -1169,9 +1169,9 @@
   <conditionalFormatting sqref="2:21">
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="-3.19"/>
+        <cfvo type="num" val="-3.18"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5.57"/>
+        <cfvo type="num" val="5.58"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1179,9 +1179,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="num" val="-1.63"/>
+        <cfvo type="num" val="-1.68"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="3.96"/>
+        <cfvo type="num" val="4.05"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1189,9 +1189,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="num" val="-0.84"/>
+        <cfvo type="num" val="-0.87"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.37"/>
+        <cfvo type="num" val="0.39"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
@@ -1199,9 +1199,9 @@
     </cfRule>
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="-1.96"/>
+        <cfvo type="num" val="-1.95"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.84"/>
+        <cfvo type="num" val="0.83"/>
         <color rgb="FF086788"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFDD1C1A"/>
